--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484316_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484316_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.1036</v>
+        <v>8.888400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.6823</v>
+        <v>7.6305</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4213</v>
+        <v>1.2579</v>
       </c>
       <c r="G2" t="n">
         <v>0.4013</v>
@@ -610,13 +610,13 @@
         <v>3.1255</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4251</v>
+        <v>1.2099</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8023</v>
+        <v>0.7506</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6228</v>
+        <v>0.4593</v>
       </c>
       <c r="V2" t="n">
         <v>4.5424</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5241</v>
+        <v>3.1595</v>
       </c>
       <c r="E3" t="n">
-        <v>1.595</v>
+        <v>1.2304</v>
       </c>
       <c r="F3" t="n">
         <v>1.9291</v>
@@ -688,10 +688,10 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.018</v>
+        <v>0.6534</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6962</v>
+        <v>0.3316</v>
       </c>
       <c r="U3" t="n">
         <v>0.3218</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6764</v>
+        <v>1.7139</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.66</v>
+        <v>-0.3774</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3364</v>
+        <v>2.0913</v>
       </c>
       <c r="G4" t="n">
         <v>1.342</v>
@@ -766,13 +766,13 @@
         <v>2.5395</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4831</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.22</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.458</v>
       </c>
       <c r="V4" t="n">
         <v>1.2186</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9147</v>
+        <v>1.0085</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2027</v>
+        <v>0.3237</v>
       </c>
       <c r="F5" t="n">
-        <v>0.712</v>
+        <v>0.6847</v>
       </c>
       <c r="G5" t="n">
         <v>0.6694</v>
@@ -844,13 +844,13 @@
         <v>0.7814</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8133</v>
+        <v>-0.7195</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4842</v>
+        <v>-0.3631</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3291</v>
+        <v>-0.3564</v>
       </c>
       <c r="V5" t="n">
         <v>0.2772</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,37 +877,37 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.925</v>
+        <v>-0.6223</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1299</v>
+        <v>0.6535</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.795</v>
+        <v>-1.2758</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1446</v>
+        <v>0.9107</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5249</v>
+        <v>1.329</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6196</v>
+        <v>-0.4183</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5635</v>
+        <v>2.2793</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1036</v>
+        <v>1.6181</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4599</v>
+        <v>0.6613</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7081</v>
+        <v>-1.3686</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.2891</v>
       </c>
       <c r="O6" t="n">
         <v>-1.0795</v>
@@ -916,34 +916,34 @@
         <v>-0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3674</v>
+        <v>-1.9534</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6818</v>
+        <v>-0.8289</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5447</v>
+        <v>-0.5041</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1371</v>
+        <v>-0.3247</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0968</v>
+        <v>-0.5088</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0.8317</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1219</v>
+        <v>-1.3405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0992</v>
+        <v>-0.6428</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0806</v>
+        <v>0.2339</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0186</v>
+        <v>-0.8767</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9782</v>
+        <v>-1.1446</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.614</v>
+        <v>-0.5249</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3642</v>
+        <v>-0.6196</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0405</v>
+        <v>0.5635</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.1036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>0.4599</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0186</v>
+        <v>-1.7081</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.614</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4047</v>
+        <v>-1.0795</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.121</v>
+        <v>-0.3997</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.121</v>
+        <v>-0.1808</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.2188</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.0968</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1228</v>
+        <v>-0.7356</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3708</v>
+        <v>-0.8541</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4936</v>
+        <v>0.1184</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9107</v>
+        <v>-1.9874</v>
       </c>
       <c r="H8" t="n">
-        <v>1.329</v>
+        <v>-0.0591</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4183</v>
+        <v>-1.9283</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2793</v>
+        <v>-0.8838</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6181</v>
+        <v>0.3697</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6613</v>
+        <v>-1.2535</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3686</v>
+        <v>-1.1036</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2891</v>
+        <v>-0.4287</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0795</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1953</v>
+        <v>1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3294</v>
+        <v>-0.6617</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.2475</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5426</v>
+        <v>-0.4142</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5088</v>
+        <v>0.1554</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3405</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5063</v>
+        <v>-0.9981</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3796</v>
+        <v>0.0205</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1267</v>
+        <v>-1.0186</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9874</v>
+        <v>-0.9782</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0591</v>
+        <v>-0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9283</v>
+        <v>-0.3642</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8838</v>
+        <v>0.0405</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3697</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2535</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1036</v>
+        <v>-1.0186</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4287</v>
+        <v>-0.614</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.4047</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4323</v>
+        <v>-0.0199</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.773</v>
+        <v>-0.0199</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6593</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1554</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6479</v>
+        <v>-1.3052</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0343</v>
+        <v>-1.6099</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3863</v>
+        <v>0.3046</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8017</v>
@@ -1234,13 +1234,13 @@
         <v>2.7348</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2757</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1594</v>
+        <v>0.2649</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4351</v>
+        <v>0.3534</v>
       </c>
       <c r="V10" t="n">
         <v>0.4875</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1985</v>
+        <v>-1.4629</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0613</v>
+        <v>-1.4347</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1371</v>
+        <v>-0.0282</v>
       </c>
       <c r="G11" t="n">
         <v>0.6918</v>
@@ -1312,13 +1312,13 @@
         <v>2.1488</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4996</v>
+        <v>0.2359</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6657</v>
+        <v>-0.0391</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1661</v>
+        <v>0.2751</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2186</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4799</v>
+        <v>-4.5538</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0875</v>
+        <v>-3.1886</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3924</v>
+        <v>-1.3652</v>
       </c>
       <c r="G12" t="n">
         <v>-0.7853</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1634</v>
+        <v>-0.2373</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1294</v>
+        <v>0.0283</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2928</v>
+        <v>-0.2656</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7731</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.239200000000002</v>
+        <v>4.449600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4176</v>
+        <v>2.627800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.821699999999999</v>
+        <v>1.8215</v>
       </c>
       <c r="G13" t="n">
         <v>-4.116400000000001</v>
@@ -1441,7 +1441,7 @@
         <v>-2.0212</v>
       </c>
       <c r="J13" t="n">
-        <v>7.568600000000001</v>
+        <v>7.5686</v>
       </c>
       <c r="K13" t="n">
         <v>4.1903</v>
@@ -1468,13 +1468,13 @@
         <v>19.5344</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8388999999999995</v>
+        <v>0.3712999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1269</v>
+        <v>0.08360000000000015</v>
       </c>
       <c r="U13" t="n">
-        <v>0.288</v>
+        <v>0.2878999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>5.2645</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.9494</v>
+        <v>5.1543</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5928</v>
+        <v>2.3905</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3566</v>
+        <v>2.7638</v>
       </c>
       <c r="G14" t="n">
         <v>4.1568</v>
@@ -1546,13 +1546,13 @@
         <v>2.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7814</v>
+        <v>-0.5764</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0384</v>
+        <v>-0.2406</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.743</v>
+        <v>-0.3358</v>
       </c>
       <c r="V14" t="n">
         <v>2.16</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6086</v>
+        <v>3.7019</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4978</v>
+        <v>3.7001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1108</v>
+        <v>0.0019</v>
       </c>
       <c r="G15" t="n">
         <v>2.2322</v>
@@ -1624,13 +1624,13 @@
         <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5184</v>
+        <v>-0.4251</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.524</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2079</v>
+        <v>0.0989</v>
       </c>
       <c r="V15" t="n">
         <v>0.3321</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.701</v>
+        <v>0.8358</v>
       </c>
       <c r="E16" t="n">
         <v>-1.4244</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1254</v>
+        <v>2.2603</v>
       </c>
       <c r="G16" t="n">
         <v>1.166</v>
@@ -1702,13 +1702,13 @@
         <v>2.7348</v>
       </c>
       <c r="S16" t="n">
-        <v>0.121</v>
+        <v>0.2559</v>
       </c>
       <c r="T16" t="n">
         <v>0.0359</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0851</v>
+        <v>0.22</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1155</v>
+        <v>0.1972</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1807</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2962</v>
+        <v>0.3779</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2086</v>
@@ -1780,13 +1780,13 @@
         <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.0151</v>
       </c>
       <c r="T17" t="n">
         <v>-0.2421</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1755</v>
+        <v>0.2572</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.17</v>
+        <v>0.1602</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2755</v>
+        <v>-0.6069</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1055</v>
+        <v>0.7671</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0291</v>
+        <v>-0.8587</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0289</v>
+        <v>0.4226</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0002</v>
+        <v>-1.2813</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0409</v>
+        <v>0.1051</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0409</v>
+        <v>1.2509</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-1.1459</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.9638</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0698</v>
+        <v>-0.8283</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0002</v>
+        <v>-0.1354</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0545</v>
+        <v>-0.0825</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.121</v>
+        <v>0.1363</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1755</v>
+        <v>-0.2188</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.8828</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.272</v>
+        <v>-0.0883</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1968</v>
+        <v>-0.2755</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4687</v>
+        <v>0.1872</v>
       </c>
       <c r="G19" t="n">
-        <v>2.9356</v>
+        <v>-0.0291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9903</v>
+        <v>-0.0289</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0547</v>
+        <v>-0.0002</v>
       </c>
       <c r="J19" t="n">
-        <v>2.7415</v>
+        <v>0.0409</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6605</v>
+        <v>0.0409</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1942</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3298</v>
+        <v>-0.0698</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1356</v>
+        <v>-0.0002</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0326</v>
+        <v>0.1362</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3494</v>
+        <v>-0.121</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3168</v>
+        <v>0.2572</v>
       </c>
       <c r="V19" t="n">
-        <v>-4.5424</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-4.5424</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5827</v>
+        <v>-0.2539</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2136</v>
+        <v>2.2979</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6309</v>
+        <v>-2.5518</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8587</v>
+        <v>2.9356</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4226</v>
+        <v>2.9903</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2813</v>
+        <v>-0.0547</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1051</v>
+        <v>2.7415</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2509</v>
+        <v>2.6605</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1459</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9638</v>
+        <v>0.1942</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8283</v>
+        <v>0.3298</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1354</v>
+        <v>-0.1356</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3441</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8254</v>
+        <v>-0.0145</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4704</v>
+        <v>-0.2482</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.355</v>
+        <v>0.2337</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8828</v>
+        <v>-4.5424</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3869</v>
+        <v>-4.5424</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3591</v>
+        <v>-1.7479</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3541</v>
+        <v>-0.9608</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.005</v>
+        <v>-0.7871</v>
       </c>
       <c r="G21" t="n">
         <v>0.3487</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1908</v>
+        <v>0.802</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0594</v>
+        <v>0.4527</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1315</v>
+        <v>0.3494</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5545</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7121</v>
+        <v>-2.2393</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2166</v>
+        <v>-3.8379</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9287</v>
+        <v>1.5986</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3704</v>
+        <v>0.0326</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.1829</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5132</v>
+        <v>0.2156</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5343</v>
+        <v>0.3778</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3725</v>
+        <v>-0.243</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1619</v>
+        <v>0.6208</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1639</v>
+        <v>-0.3451</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4889</v>
+        <v>0.0601</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6751</v>
+        <v>-0.4052</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1488</v>
+        <v>-3.9069</v>
       </c>
       <c r="R22" t="n">
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>1.632</v>
+        <v>-0.1231</v>
       </c>
       <c r="T22" t="n">
-        <v>0.831</v>
+        <v>-0.3088</v>
       </c>
       <c r="U22" t="n">
-        <v>0.801</v>
+        <v>0.1856</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3238</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.3238</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6114</v>
+        <v>-2.3708</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.939</v>
+        <v>-0.0867</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3276</v>
+        <v>-2.2841</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0326</v>
+        <v>0.3704</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1829</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2156</v>
+        <v>-0.5132</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3778</v>
+        <v>1.5343</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.243</v>
+        <v>1.3725</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6208</v>
+        <v>0.1619</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3451</v>
+        <v>-1.1639</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0601</v>
+        <v>-0.4889</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4052</v>
+        <v>-0.6751</v>
       </c>
       <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-2.1488</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-3.9069</v>
       </c>
       <c r="R23" t="n">
         <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4952</v>
+        <v>0.9733000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4099</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0854</v>
+        <v>0.4456</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-3.3238</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-3.3238</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9065</v>
+        <v>-5.9144</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2156</v>
+        <v>-3.1145</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6909</v>
+        <v>-2.7999</v>
       </c>
       <c r="G24" t="n">
         <v>-6.0294</v>
@@ -2326,13 +2326,13 @@
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5601</v>
+        <v>0.5523</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1432</v>
+        <v>0.2443</v>
       </c>
       <c r="U24" t="n">
-        <v>0.417</v>
+        <v>0.308</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2186</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.239300000000001</v>
+        <v>-2.565199999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-2.0989</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.140300000000001</v>
+        <v>-0.4661000000000004</v>
       </c>
       <c r="G25" t="n">
         <v>4.116499999999999</v>
@@ -2374,7 +2374,7 @@
         <v>2.0951</v>
       </c>
       <c r="I25" t="n">
-        <v>2.021300000000001</v>
+        <v>2.0213</v>
       </c>
       <c r="J25" t="n">
         <v>11.6851</v>
@@ -2386,10 +2386,10 @@
         <v>5.399700000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.568499999999999</v>
+        <v>-7.5685</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.1902</v>
+        <v>-4.190200000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-3.3784</v>
@@ -2404,13 +2404,13 @@
         <v>16.6041</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8388000000000002</v>
+        <v>1.5132</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2879999999999999</v>
+        <v>-0.2878000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1269</v>
+        <v>1.801</v>
       </c>
       <c r="V25" t="n">
         <v>-5.2644</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484316_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484316_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,7 +646,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>-0.1219</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,74 +729,79 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7139</v>
+        <v>1.214</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3774</v>
+        <v>1.214</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0913</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.342</v>
+        <v>1.214</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5467</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8887</v>
+        <v>1.214</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9709</v>
+        <v>1.214</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8891</v>
+        <v>1.214</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5207000000000001</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.06270000000000001</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.458</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -792,7 +812,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -860,1089 +880,1155 @@
       </c>
       <c r="X5" t="n">
         <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>P. CARRION SORIANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6223</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6535</v>
+        <v>-1.5913</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2758</v>
+        <v>2.0913</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9107</v>
+        <v>0.128</v>
       </c>
       <c r="H6" t="n">
-        <v>1.329</v>
+        <v>-0.5467</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4183</v>
+        <v>0.6747</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2793</v>
+        <v>0.757</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6181</v>
+        <v>0.0819</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6613</v>
+        <v>0.6751</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3686</v>
+        <v>-0.6289</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2891</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0795</v>
+        <v>-0.0004</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7581</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8289</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5041</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3247</v>
+        <v>0.458</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5088</v>
+        <v>1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8317</v>
+        <v>1.4959</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3405</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6428</v>
+        <v>0.307</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2339</v>
+        <v>0.307</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8767</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1446</v>
+        <v>0.307</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5249</v>
+        <v>0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6196</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5635</v>
+        <v>0.307</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1036</v>
+        <v>0.307</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7081</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0795</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3997</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1808</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2188</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0968</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1219</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7356</v>
+        <v>-0.6428</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8541</v>
+        <v>0.2339</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1184</v>
+        <v>-0.8767</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9874</v>
+        <v>-1.1446</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0591</v>
+        <v>-0.5249</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9283</v>
+        <v>-0.6196</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8838</v>
+        <v>0.5635</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3697</v>
+        <v>0.1036</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2535</v>
+        <v>0.4599</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1036</v>
+        <v>-1.7081</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4287</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-1.0795</v>
       </c>
       <c r="P8" t="n">
-        <v>1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3674</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6617</v>
+        <v>-0.3997</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2475</v>
+        <v>-0.1808</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4142</v>
+        <v>-0.2188</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1554</v>
+        <v>1.0968</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
         <v>-0.1219</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. POCULL DURAN</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9981</v>
+        <v>-0.7356</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0205</v>
+        <v>-0.8541</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0186</v>
+        <v>0.1184</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9782</v>
+        <v>-1.9874</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.614</v>
+        <v>-0.0591</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3642</v>
+        <v>-1.9283</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0405</v>
+        <v>-0.8838</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.3697</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>-1.2535</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0186</v>
+        <v>-1.1036</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.614</v>
+        <v>-0.4287</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4047</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0199</v>
+        <v>-0.6617</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0199</v>
+        <v>-0.2475</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0.4142</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1554</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3052</v>
+        <v>-0.9292</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6099</v>
+        <v>0.3465</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3046</v>
+        <v>-1.2758</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8017</v>
+        <v>0.6037</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9936</v>
+        <v>1.022</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8081</v>
+        <v>-0.4183</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3586</v>
+        <v>1.9723</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2254</v>
+        <v>1.3111</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1332</v>
+        <v>0.6613</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4431</v>
+        <v>-1.3686</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7682</v>
+        <v>-0.2891</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-1.0795</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3441</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7348</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6183999999999999</v>
+        <v>-0.8289</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2649</v>
+        <v>-0.5041</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3534</v>
+        <v>-0.3247</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4875</v>
+        <v>-0.5088</v>
       </c>
       <c r="W10" t="n">
-        <v>1.8279</v>
+        <v>0.8317</v>
       </c>
       <c r="X10" t="n">
         <v>-1.3405</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>L. POCULL DURAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4629</v>
+        <v>-0.9981</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4347</v>
+        <v>0.0205</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0282</v>
+        <v>-1.0186</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6918</v>
+        <v>-0.9782</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1364</v>
+        <v>-0.614</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4445</v>
+        <v>-0.3642</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9252</v>
+        <v>0.0405</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9647</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0395</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2334</v>
+        <v>-1.0186</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8283</v>
+        <v>-0.614</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4051</v>
+        <v>-0.4047</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.3208</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2359</v>
+        <v>-0.0199</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0391</v>
+        <v>-0.0199</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2751</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5538</v>
+        <v>-1.3052</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1886</v>
+        <v>-1.6099</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3652</v>
+        <v>0.3046</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7853</v>
+        <v>-2.8017</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0565</v>
+        <v>-1.9936</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.7288</v>
+        <v>-0.8081</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1039</v>
+        <v>-1.3586</v>
       </c>
       <c r="K12" t="n">
-        <v>0.023</v>
+        <v>-1.2254</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0809</v>
+        <v>-0.1332</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8893</v>
+        <v>-1.4431</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0795</v>
+        <v>-0.7682</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8097</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.3208</v>
+        <v>-2.3441</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2373</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0283</v>
+        <v>0.2649</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2656</v>
+        <v>0.3534</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7731</v>
+        <v>0.4875</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7731</v>
+        <v>-1.3405</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.449600000000001</v>
+        <v>-1.4629</v>
       </c>
       <c r="E13" t="n">
-        <v>2.627800000000001</v>
+        <v>-1.4347</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8215</v>
+        <v>-0.0282</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.116400000000001</v>
+        <v>0.6918</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.095</v>
+        <v>1.1364</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.0212</v>
+        <v>-0.4445</v>
       </c>
       <c r="J13" t="n">
-        <v>7.5686</v>
+        <v>1.9252</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1903</v>
+        <v>1.9647</v>
       </c>
       <c r="L13" t="n">
-        <v>3.378400000000001</v>
+        <v>-0.0395</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.6851</v>
+        <v>-1.2334</v>
       </c>
       <c r="N13" t="n">
-        <v>-6.285200000000001</v>
+        <v>-0.8283</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.3996</v>
+        <v>-0.4051</v>
       </c>
       <c r="P13" t="n">
-        <v>2.9302</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q13" t="n">
-        <v>-16.6041</v>
+        <v>-3.3208</v>
       </c>
       <c r="R13" t="n">
-        <v>19.5344</v>
+        <v>2.1488</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3712999999999999</v>
+        <v>0.2359</v>
       </c>
       <c r="T13" t="n">
-        <v>0.08360000000000015</v>
+        <v>-0.0391</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2878999999999999</v>
+        <v>0.2751</v>
       </c>
       <c r="V13" t="n">
-        <v>5.2645</v>
+        <v>-1.2186</v>
       </c>
       <c r="W13" t="n">
-        <v>11.5798</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.3156</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.1543</v>
+        <v>-4.5538</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3905</v>
+        <v>-3.1886</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7638</v>
+        <v>-1.3652</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1568</v>
+        <v>-0.7853</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5541</v>
+        <v>-0.0565</v>
       </c>
       <c r="I14" t="n">
-        <v>2.6026</v>
+        <v>-0.7288</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6515</v>
+        <v>0.1039</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0478</v>
+        <v>0.023</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6036</v>
+        <v>0.0809</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4947</v>
+        <v>-0.8893</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4937</v>
+        <v>-0.0795</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.001</v>
+        <v>-0.8097</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.5162</v>
+        <v>-3.3208</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9301</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5764</v>
+        <v>-0.2373</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2406</v>
+        <v>0.0283</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3358</v>
+        <v>-0.2656</v>
       </c>
       <c r="V14" t="n">
-        <v>2.16</v>
+        <v>-1.7731</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7019</v>
+        <v>4.449800000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7001</v>
+        <v>2.627899999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0019</v>
+        <v>1.821499999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2322</v>
+        <v>-4.116400000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5863</v>
+        <v>-2.095</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6459</v>
+        <v>-2.0212</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7868</v>
+        <v>7.568700000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0054</v>
+        <v>4.1903</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7815</v>
+        <v>3.3784</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5546</v>
+        <v>-11.6851</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.419</v>
+        <v>-6.285200000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1356</v>
+        <v>-5.3996</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>2.9302</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3907</v>
+        <v>-16.6041</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9534</v>
+        <v>19.5344</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4251</v>
+        <v>0.3713</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.524</v>
+        <v>0.08360000000000006</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0989</v>
+        <v>0.2878999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3321</v>
+        <v>5.2645</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8279</v>
+        <v>11.5798</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
-      </c>
+        <v>-6.3156</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8358</v>
+        <v>5.1543</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4244</v>
+        <v>2.3905</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2603</v>
+        <v>2.7638</v>
       </c>
       <c r="G16" t="n">
-        <v>1.166</v>
+        <v>4.1568</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.8417</v>
+        <v>1.5541</v>
       </c>
       <c r="I16" t="n">
-        <v>3.0077</v>
+        <v>2.6026</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8605</v>
+        <v>4.6515</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.283</v>
+        <v>2.0478</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1435</v>
+        <v>2.6036</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6945</v>
+        <v>-0.4947</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5587</v>
+        <v>-0.4937</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1358</v>
+        <v>-0.001</v>
       </c>
       <c r="P16" t="n">
         <v>-0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.3208</v>
+        <v>-3.5162</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7348</v>
+        <v>2.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2559</v>
+        <v>-0.5764</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0359</v>
+        <v>-0.2406</v>
       </c>
       <c r="U16" t="n">
-        <v>0.22</v>
+        <v>-0.3358</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. TURNQUEST</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1972</v>
+        <v>2.7879</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1807</v>
+        <v>2.7861</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3779</v>
+        <v>0.0019</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2086</v>
+        <v>1.3182</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1962</v>
+        <v>0.2793</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4049</v>
+        <v>1.0389</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0614</v>
+        <v>1.8729</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0614</v>
+        <v>0.6984</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.1745</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.27</v>
+        <v>-0.5546</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1348</v>
+        <v>-0.419</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4049</v>
+        <v>-0.1356</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.3907</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0151</v>
+        <v>-0.4251</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2421</v>
+        <v>-0.524</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2572</v>
+        <v>0.0989</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>R. PALOMARES MUÑOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1602</v>
+        <v>0.914</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6069</v>
+        <v>0.914</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7671</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8587</v>
+        <v>0.914</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4226</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2813</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1051</v>
+        <v>0.914</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2509</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.1459</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9638</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8283</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0825</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1363</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2188</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8828</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0883</v>
+        <v>0.614</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2755</v>
+        <v>0.614</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1872</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0291</v>
+        <v>0.614</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0289</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0409</v>
+        <v>0.614</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0409</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0002</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1362</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.121</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2572</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,231 +2038,246 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2539</v>
+        <v>0.5288</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2979</v>
+        <v>-1.7314</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5518</v>
+        <v>2.2603</v>
       </c>
       <c r="G20" t="n">
-        <v>2.9356</v>
+        <v>0.859</v>
       </c>
       <c r="H20" t="n">
-        <v>2.9903</v>
+        <v>-2.1487</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0547</v>
+        <v>3.0077</v>
       </c>
       <c r="J20" t="n">
-        <v>2.7415</v>
+        <v>1.5535</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6605</v>
+        <v>-1.59</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>3.1435</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1942</v>
+        <v>-0.6945</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3298</v>
+        <v>-0.5587</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1356</v>
+        <v>-0.1358</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3674</v>
+        <v>-0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1953</v>
+        <v>-3.3208</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0145</v>
+        <v>0.2559</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2482</v>
+        <v>0.0359</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2337</v>
+        <v>0.22</v>
       </c>
       <c r="V20" t="n">
-        <v>-4.5424</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.5424</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7479</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9608</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7871</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3487</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>0.295</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0537</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.712</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9836</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7284</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3634</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6887</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6747</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4527</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3494</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>E. TURNQUEST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2393</v>
+        <v>0.1972</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8379</v>
+        <v>-0.1807</v>
       </c>
       <c r="F22" t="n">
-        <v>1.5986</v>
+        <v>0.3779</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0326</v>
+        <v>-0.2086</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1829</v>
+        <v>0.1962</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2156</v>
+        <v>-0.4049</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3778</v>
+        <v>0.0614</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.243</v>
+        <v>0.0614</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6208</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3451</v>
+        <v>-0.27</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0601</v>
+        <v>0.1348</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4052</v>
+        <v>-0.4049</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.1488</v>
+        <v>0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1231</v>
+        <v>0.0151</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3088</v>
+        <v>-0.2421</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1856</v>
+        <v>0.2572</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2186,241 +2287,672 @@
       </c>
       <c r="X22" t="n">
         <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3708</v>
+        <v>-0.0883</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0867</v>
+        <v>-0.2755</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2841</v>
+        <v>0.1872</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3704</v>
+        <v>-0.0291</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8836000000000001</v>
+        <v>-0.0289</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5132</v>
+        <v>-0.0002</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5343</v>
+        <v>0.0409</v>
       </c>
       <c r="K23" t="n">
-        <v>1.3725</v>
+        <v>0.0409</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1639</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4889</v>
+        <v>-0.0698</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6751</v>
+        <v>-0.0002</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.1362</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.121</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4456</v>
+        <v>0.2572</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.3238</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.3238</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9144</v>
+        <v>-0.2539</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1145</v>
+        <v>2.2979</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7999</v>
+        <v>-2.5518</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.0294</v>
+        <v>2.9356</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7795</v>
+        <v>2.9903</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.2499</v>
+        <v>-0.0547</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.1867</v>
+        <v>2.7415</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6117</v>
+        <v>2.6605</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.575</v>
+        <v>0.0809</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8427</v>
+        <v>0.1942</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1678</v>
+        <v>0.3298</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.1356</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5523</v>
+        <v>-0.0145</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2443</v>
+        <v>-0.2482</v>
       </c>
       <c r="U24" t="n">
-        <v>0.308</v>
+        <v>0.2337</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2186</v>
+        <v>-4.5424</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.4373</v>
+        <v>-4.5424</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-0.4538</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.2209</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.7671</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.4726</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.1914</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.2813</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.5089</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.1459</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.9638</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.8283</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.1354</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0825</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.2188</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.8828</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>R. DALET CASALPRIM</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.7479</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.9608</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.7871</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.0537</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.712</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.7284</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.3634</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.6887</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6747</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.3441</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.1255</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>R. FERNANDEZ DIAZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.2393</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.8379</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.5986</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-0.1829</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2156</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-0.243</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6208</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.3451</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0601</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.4052</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3.9069</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.1231</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.3088</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.1856</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>V. MANDIM SILVA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.3708</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.0867</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.2841</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.8836000000000001</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.5132</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.5343</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1.3725</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1.1639</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.4889</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-0.6751</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.9733000000000001</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.5276999999999999</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.4456</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>J. LLORENTE GUILLEMI</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-5.9144</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-3.1145</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.7999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-6.0294</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-2.7795</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-3.2499</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-4.1867</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-1.6117</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-2.575</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1.8427</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-1.1678</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-0.6749000000000001</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.5523</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.2443</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="V29" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X29" t="n">
+        <v>-2.4373</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>play_by_play_2484316_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>-2.565199999999999</v>
       </c>
-      <c r="E25" t="n">
-        <v>-2.0989</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="E30" t="n">
+        <v>-2.098900000000002</v>
+      </c>
+      <c r="F30" t="n">
         <v>-0.4661000000000004</v>
       </c>
-      <c r="G25" t="n">
-        <v>4.116499999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.0951</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="G30" t="n">
+        <v>4.116600000000003</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.095100000000001</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.0213</v>
       </c>
-      <c r="J25" t="n">
-        <v>11.6851</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6.2853</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5.399700000000001</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="J30" t="n">
+        <v>11.6852</v>
+      </c>
+      <c r="K30" t="n">
+        <v>6.2854</v>
+      </c>
+      <c r="L30" t="n">
+        <v>5.3997</v>
+      </c>
+      <c r="M30" t="n">
         <v>-7.5685</v>
       </c>
-      <c r="N25" t="n">
-        <v>-4.190200000000001</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="N30" t="n">
+        <v>-4.1902</v>
+      </c>
+      <c r="O30" t="n">
         <v>-3.3784</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P30" t="n">
         <v>-2.9301</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q30" t="n">
         <v>-19.5343</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R30" t="n">
         <v>16.6041</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S30" t="n">
         <v>1.5132</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T30" t="n">
         <v>-0.2878000000000002</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U30" t="n">
         <v>1.801</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V30" t="n">
         <v>-5.2644</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W30" t="n">
         <v>6.0383</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X30" t="n">
         <v>-11.3028</v>
       </c>
+      <c r="Y30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
